--- a/SWTest/Outputs/Finalists/AMT_Analysis_Final.xlsx
+++ b/SWTest/Outputs/Finalists/AMT_Analysis_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\Finalists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646C99D8-422F-431A-A78C-391FD7E2F83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F9C8D3-70C1-41C4-9A0E-BC39B0CA9812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="375" windowWidth="28455" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AMT" sheetId="1" r:id="rId1"/>
@@ -1891,26 +1891,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O173"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="93.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="6" customWidth="1"/>
-    <col min="14" max="14" width="20.5703125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="255.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="93.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="86.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="255.6640625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>234</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -1998,7 +1998,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
     </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
@@ -2039,7 +2039,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
@@ -2080,7 +2080,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
     </row>
-    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
     </row>
-    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2162,7 +2162,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>24</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>30</v>
       </c>
@@ -2291,7 +2291,7 @@
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
     </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>191</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>354</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>12</v>
       </c>
@@ -2416,7 +2416,7 @@
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
     </row>
-    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
@@ -2455,7 +2455,7 @@
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
     </row>
-    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>324</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>32</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>33</v>
       </c>
@@ -2586,7 +2586,7 @@
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>70</v>
       </c>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>35</v>
       </c>
@@ -2672,7 +2672,7 @@
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>269</v>
       </c>
@@ -2711,7 +2711,7 @@
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>48</v>
       </c>
@@ -2750,7 +2750,7 @@
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
     </row>
-    <row r="21" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>45</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>139</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>52</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>284</v>
       </c>
@@ -2916,7 +2916,7 @@
       <c r="N24" s="9"/>
       <c r="O24" s="9"/>
     </row>
-    <row r="25" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>43</v>
       </c>
@@ -2959,7 +2959,7 @@
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
     </row>
-    <row r="26" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>55</v>
       </c>
@@ -3002,7 +3002,7 @@
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
     </row>
-    <row r="27" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>217</v>
       </c>
@@ -3043,7 +3043,7 @@
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
     </row>
-    <row r="28" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>50</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>260</v>
       </c>
@@ -3172,7 +3172,7 @@
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
     </row>
-    <row r="31" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>267</v>
       </c>
@@ -3213,7 +3213,7 @@
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>143</v>
       </c>
@@ -3254,7 +3254,7 @@
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>145</v>
       </c>
@@ -3295,7 +3295,7 @@
       <c r="N33" s="9"/>
       <c r="O33" s="9"/>
     </row>
-    <row r="34" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>147</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
     </row>
-    <row r="35" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>149</v>
       </c>
@@ -3377,7 +3377,7 @@
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
     </row>
-    <row r="36" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>57</v>
       </c>
@@ -3420,7 +3420,7 @@
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
     </row>
-    <row r="37" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>59</v>
       </c>
@@ -3463,7 +3463,7 @@
       <c r="N37" s="9"/>
       <c r="O37" s="9"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>61</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>63</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>287</v>
       </c>
@@ -3592,7 +3592,7 @@
       <c r="N40" s="9"/>
       <c r="O40" s="9"/>
     </row>
-    <row r="41" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>288</v>
       </c>
@@ -3633,7 +3633,7 @@
       <c r="N41" s="9"/>
       <c r="O41" s="9"/>
     </row>
-    <row r="42" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>67</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="N42" s="9"/>
       <c r="O42" s="9"/>
     </row>
-    <row r="43" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>208</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="N43" s="9"/>
       <c r="O43" s="9"/>
     </row>
-    <row r="44" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>69</v>
       </c>
@@ -3754,7 +3754,7 @@
       <c r="N44" s="9"/>
       <c r="O44" s="9"/>
     </row>
-    <row r="45" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>352</v>
       </c>
@@ -3793,7 +3793,7 @@
       <c r="N45" s="9"/>
       <c r="O45" s="9"/>
     </row>
-    <row r="46" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>84</v>
       </c>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O46" s="9"/>
     </row>
-    <row r="47" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>355</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>320</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>127</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>66</v>
       </c>
@@ -4002,7 +4002,7 @@
       <c r="N50" s="9"/>
       <c r="O50" s="9"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>186</v>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="N51" s="9"/>
       <c r="O51" s="9"/>
     </row>
-    <row r="52" spans="1:15" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>263</v>
       </c>
@@ -4088,7 +4088,7 @@
       <c r="N52" s="9"/>
       <c r="O52" s="9"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>366</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>365</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>37</v>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="N55" s="9"/>
       <c r="O55" s="9"/>
     </row>
-    <row r="56" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>38</v>
       </c>
@@ -4252,7 +4252,7 @@
       <c r="N56" s="9"/>
       <c r="O56" s="9"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>39</v>
       </c>
@@ -4293,7 +4293,7 @@
       <c r="N57" s="9"/>
       <c r="O57" s="9"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>76</v>
       </c>
@@ -4334,7 +4334,7 @@
       <c r="N58" s="9"/>
       <c r="O58" s="9"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>331</v>
       </c>
@@ -4375,7 +4375,7 @@
       <c r="N59" s="9"/>
       <c r="O59" s="9"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>418</v>
       </c>
@@ -4416,7 +4416,7 @@
       <c r="N60" s="9"/>
       <c r="O60" s="9"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>78</v>
       </c>
@@ -4457,7 +4457,7 @@
       <c r="N61" s="9"/>
       <c r="O61" s="9"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>80</v>
       </c>
@@ -4498,7 +4498,7 @@
       <c r="N62" s="9"/>
       <c r="O62" s="9"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>91</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>96</v>
       </c>
@@ -4582,7 +4582,7 @@
       <c r="N64" s="9"/>
       <c r="O64" s="9"/>
     </row>
-    <row r="65" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>86</v>
       </c>
@@ -4625,7 +4625,7 @@
       <c r="N65" s="9"/>
       <c r="O65" s="9"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>95</v>
       </c>
@@ -4666,7 +4666,7 @@
       <c r="N66" s="9"/>
       <c r="O66" s="9"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>98</v>
       </c>
@@ -4707,7 +4707,7 @@
       <c r="N67" s="9"/>
       <c r="O67" s="9"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>89</v>
       </c>
@@ -4748,7 +4748,7 @@
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>165</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>129</v>
       </c>
@@ -4834,7 +4834,7 @@
       <c r="N70" s="9"/>
       <c r="O70" s="9"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>106</v>
       </c>
@@ -4873,7 +4873,7 @@
       <c r="N71" s="9"/>
       <c r="O71" s="9"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>329</v>
       </c>
@@ -4914,7 +4914,7 @@
       <c r="N72" s="9"/>
       <c r="O72" s="9"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>102</v>
       </c>
@@ -4955,7 +4955,7 @@
       <c r="N73" s="9"/>
       <c r="O73" s="9"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>121</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="N74" s="9"/>
       <c r="O74" s="9"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>100</v>
       </c>
@@ -5037,7 +5037,7 @@
       <c r="N75" s="9"/>
       <c r="O75" s="9"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>114</v>
       </c>
@@ -5078,7 +5078,7 @@
       <c r="N76" s="9"/>
       <c r="O76" s="9"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>116</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
         <v>108</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
         <v>118</v>
       </c>
@@ -5203,7 +5203,7 @@
       <c r="N79" s="9"/>
       <c r="O79" s="9"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
         <v>399</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>286</v>
       </c>
@@ -5287,7 +5287,7 @@
       <c r="N81" s="9"/>
       <c r="O81" s="9"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>328</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>124</v>
       </c>
@@ -5371,7 +5371,7 @@
       <c r="N83" s="9"/>
       <c r="O83" s="9"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
         <v>85</v>
       </c>
@@ -5414,7 +5414,7 @@
       <c r="N84" s="9"/>
       <c r="O84" s="9"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
         <v>190</v>
       </c>
@@ -5457,7 +5457,7 @@
       <c r="N85" s="9"/>
       <c r="O85" s="9"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
         <v>261</v>
       </c>
@@ -5500,7 +5500,7 @@
       <c r="N86" s="9"/>
       <c r="O86" s="9"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
         <v>117</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
         <v>120</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
         <v>407</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
         <v>273</v>
       </c>
@@ -5670,7 +5670,7 @@
       <c r="N90" s="9"/>
       <c r="O90" s="9"/>
     </row>
-    <row r="91" spans="1:15" s="3" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
         <v>281</v>
       </c>
@@ -5709,7 +5709,7 @@
       <c r="N91" s="9"/>
       <c r="O91" s="9"/>
     </row>
-    <row r="92" spans="1:15" s="3" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9" t="s">
         <v>40</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:15" s="3" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" s="3" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9" t="s">
         <v>304</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="N93" s="9"/>
       <c r="O93" s="9"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
         <v>210</v>
       </c>
@@ -5836,7 +5836,7 @@
       <c r="N94" s="9"/>
       <c r="O94" s="9"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
         <v>125</v>
       </c>
@@ -5877,7 +5877,7 @@
       <c r="N95" s="9"/>
       <c r="O95" s="9"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
         <v>211</v>
       </c>
@@ -5918,7 +5918,7 @@
       <c r="N96" s="9"/>
       <c r="O96" s="9"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
         <v>337</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="N97" s="9"/>
       <c r="O97" s="9"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
         <v>336</v>
       </c>
@@ -6000,7 +6000,7 @@
       <c r="N98" s="9"/>
       <c r="O98" s="9"/>
     </row>
-    <row r="99" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
         <v>213</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="N99" s="9"/>
       <c r="O99" s="9"/>
     </row>
-    <row r="100" spans="1:15" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>218</v>
       </c>
@@ -6082,7 +6082,7 @@
       <c r="N100" s="9"/>
       <c r="O100" s="9"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>338</v>
       </c>
@@ -6123,7 +6123,7 @@
       <c r="N101" s="9"/>
       <c r="O101" s="9"/>
     </row>
-    <row r="102" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>339</v>
       </c>
@@ -6164,7 +6164,7 @@
       <c r="N102" s="9"/>
       <c r="O102" s="9"/>
     </row>
-    <row r="103" spans="1:15" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>72</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>358</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
         <v>74</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
         <v>356</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="9" t="s">
         <v>75</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9" t="s">
         <v>359</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9" t="s">
         <v>131</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
         <v>112</v>
       </c>
@@ -6496,7 +6496,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
         <v>277</v>
       </c>
@@ -6535,7 +6535,7 @@
       <c r="N111" s="9"/>
       <c r="O111" s="9"/>
     </row>
-    <row r="112" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="9" t="s">
         <v>394</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="9" t="s">
         <v>136</v>
       </c>
@@ -6617,7 +6617,7 @@
       <c r="N113" s="9"/>
       <c r="O113" s="9"/>
     </row>
-    <row r="114" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="9" t="s">
         <v>362</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
         <v>134</v>
       </c>
@@ -6699,7 +6699,7 @@
       <c r="N115" s="9"/>
       <c r="O115" s="9"/>
     </row>
-    <row r="116" spans="1:15" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="9" t="s">
         <v>275</v>
       </c>
@@ -6738,7 +6738,7 @@
       <c r="N116" s="9"/>
       <c r="O116" s="9"/>
     </row>
-    <row r="117" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="9" t="s">
         <v>221</v>
       </c>
@@ -6779,7 +6779,7 @@
       <c r="N117" s="9"/>
       <c r="O117" s="9"/>
     </row>
-    <row r="118" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
         <v>220</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="N118" s="9"/>
       <c r="O118" s="9"/>
     </row>
-    <row r="119" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
         <v>333</v>
       </c>
@@ -6861,7 +6861,7 @@
       <c r="N119" s="9"/>
       <c r="O119" s="9"/>
     </row>
-    <row r="120" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="9" t="s">
         <v>410</v>
       </c>
@@ -6902,7 +6902,7 @@
       <c r="N120" s="9"/>
       <c r="O120" s="9"/>
     </row>
-    <row r="121" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="9" t="s">
         <v>404</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9" t="s">
         <v>401</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9" t="s">
         <v>138</v>
       </c>
@@ -7029,7 +7029,7 @@
       <c r="N123" s="9"/>
       <c r="O123" s="9"/>
     </row>
-    <row r="124" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
         <v>181</v>
       </c>
@@ -7072,7 +7072,7 @@
       <c r="N124" s="9"/>
       <c r="O124" s="9"/>
     </row>
-    <row r="125" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="9" t="s">
         <v>262</v>
       </c>
@@ -7115,7 +7115,7 @@
       <c r="N125" s="9"/>
       <c r="O125" s="9"/>
     </row>
-    <row r="126" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
         <v>258</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9" t="s">
         <v>364</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
         <v>156</v>
       </c>
@@ -7242,7 +7242,7 @@
       <c r="N128" s="9"/>
       <c r="O128" s="9"/>
     </row>
-    <row r="129" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
         <v>175</v>
       </c>
@@ -7285,7 +7285,7 @@
       <c r="N129" s="9"/>
       <c r="O129" s="9"/>
     </row>
-    <row r="130" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
         <v>411</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="N130" s="9"/>
       <c r="O130" s="9"/>
     </row>
-    <row r="131" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>151</v>
       </c>
@@ -7371,7 +7371,7 @@
       <c r="N131" s="9"/>
       <c r="O131" s="9"/>
     </row>
-    <row r="132" spans="1:15" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
         <v>154</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
         <v>169</v>
       </c>
@@ -7455,7 +7455,7 @@
       <c r="N133" s="9"/>
       <c r="O133" s="9"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
         <v>219</v>
       </c>
@@ -7496,7 +7496,7 @@
       <c r="N134" s="9"/>
       <c r="O134" s="9"/>
     </row>
-    <row r="135" spans="1:15" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
         <v>341</v>
       </c>
@@ -7537,7 +7537,7 @@
       <c r="N135" s="9"/>
       <c r="O135" s="9"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
         <v>340</v>
       </c>
@@ -7578,7 +7578,7 @@
       <c r="N136" s="9"/>
       <c r="O136" s="9"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
         <v>271</v>
       </c>
@@ -7617,7 +7617,7 @@
       <c r="N137" s="9"/>
       <c r="O137" s="9"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>141</v>
       </c>
@@ -7658,7 +7658,7 @@
       <c r="N138" s="9"/>
       <c r="O138" s="9"/>
     </row>
-    <row r="139" spans="1:15" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
         <v>425</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
         <v>241</v>
       </c>
@@ -7740,7 +7740,7 @@
       <c r="N140" s="9"/>
       <c r="O140" s="9"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
         <v>426</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
         <v>166</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
         <v>167</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
         <v>168</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
         <v>8</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
         <v>77</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
         <v>360</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
         <v>423</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>158</v>
       </c>
@@ -8117,7 +8117,7 @@
       <c r="N149" s="9"/>
       <c r="O149" s="9"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
         <v>160</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
         <v>264</v>
       </c>
@@ -8199,7 +8199,7 @@
       <c r="N151" s="9"/>
       <c r="O151" s="9"/>
     </row>
-    <row r="152" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
         <v>82</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
         <v>361</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="154" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
         <v>424</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>279</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="N155" s="9"/>
       <c r="O155" s="9"/>
     </row>
-    <row r="156" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
         <v>196</v>
       </c>
@@ -8400,7 +8400,7 @@
       <c r="N156" s="9"/>
       <c r="O156" s="9"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
         <v>237</v>
       </c>
@@ -8441,7 +8441,7 @@
       <c r="N157" s="9"/>
       <c r="O157" s="9"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
         <v>348</v>
       </c>
@@ -8482,7 +8482,7 @@
       <c r="N158" s="9"/>
       <c r="O158" s="9"/>
     </row>
-    <row r="159" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
         <v>349</v>
       </c>
@@ -8523,7 +8523,7 @@
       <c r="N159" s="9"/>
       <c r="O159" s="9"/>
     </row>
-    <row r="160" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>344</v>
       </c>
@@ -8564,7 +8564,7 @@
       <c r="N160" s="9"/>
       <c r="O160" s="9"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>343</v>
       </c>
@@ -8605,7 +8605,7 @@
       <c r="N161" s="9"/>
       <c r="O161" s="9"/>
     </row>
-    <row r="162" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>342</v>
       </c>
@@ -8646,7 +8646,7 @@
       <c r="N162" s="9"/>
       <c r="O162" s="9"/>
     </row>
-    <row r="163" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>197</v>
       </c>
@@ -8685,7 +8685,7 @@
       <c r="N163" s="9"/>
       <c r="O163" s="9"/>
     </row>
-    <row r="164" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>238</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="165" spans="1:15" s="3" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" s="3" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>345</v>
       </c>
@@ -8769,7 +8769,7 @@
       <c r="N165" s="9"/>
       <c r="O165" s="9"/>
     </row>
-    <row r="166" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
         <v>350</v>
       </c>
@@ -8810,7 +8810,7 @@
       <c r="N166" s="9"/>
       <c r="O166" s="9"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
         <v>419</v>
       </c>
@@ -8851,7 +8851,7 @@
       <c r="N167" s="9"/>
       <c r="O167" s="9"/>
     </row>
-    <row r="168" spans="1:15" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" ht="73.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
         <v>420</v>
       </c>
@@ -8892,7 +8892,7 @@
       <c r="N168" s="9"/>
       <c r="O168" s="9"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
         <v>421</v>
       </c>
@@ -8933,7 +8933,7 @@
       <c r="N169" s="9"/>
       <c r="O169" s="9"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
         <v>412</v>
       </c>
@@ -8972,7 +8972,7 @@
       <c r="N170" s="9"/>
       <c r="O170" s="9"/>
     </row>
-    <row r="171" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
         <v>413</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
         <v>422</v>
       </c>
@@ -9056,7 +9056,7 @@
       <c r="N172" s="9"/>
       <c r="O172" s="9"/>
     </row>
-    <row r="173" spans="1:15" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
         <v>432</v>
       </c>

--- a/SWTest/Outputs/Finalists/AMT_Analysis_Final.xlsx
+++ b/SWTest/Outputs/Finalists/AMT_Analysis_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\Finalists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F9C8D3-70C1-41C4-9A0E-BC39B0CA9812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5546903-7882-4B0E-8426-E76B4687DF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22728" yWindow="288" windowWidth="16416" windowHeight="8856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AMT" sheetId="1" r:id="rId1"/>
@@ -1439,9 +1439,6 @@
 Future Scope (post launch): allow "spare sensor" to be configurable as "installed/not installed" via HMI/wintrac. Dependency: only display this parameter in SW data log when Spare temp. sensor is configured as installed</t>
   </si>
   <si>
-    <t>Access Level (Wintrac)</t>
-  </si>
-  <si>
     <t>Event Log When Parameter Changes?</t>
   </si>
   <si>
@@ -1449,6 +1446,9 @@
   </si>
   <si>
     <t>Auto Log at Noon (12:05 PM)?</t>
+  </si>
+  <si>
+    <t>Access Level (WinTrac)</t>
   </si>
 </sst>
 </file>
@@ -1891,26 +1891,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O173"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="93.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="86.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="255.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="93.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="6" customWidth="1"/>
+    <col min="14" max="14" width="86.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="255.7109375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>234</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>444</v>
@@ -1942,13 +1942,13 @@
         <v>1</v>
       </c>
       <c r="K1" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="L1" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>450</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>451</v>
       </c>
       <c r="N1" s="11" t="s">
         <v>2</v>
@@ -1957,7 +1957,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -1998,7 +1998,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
     </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" s="3" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
@@ -2039,7 +2039,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
@@ -2080,7 +2080,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
     </row>
-    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
     </row>
-    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>28</v>
       </c>
@@ -2162,7 +2162,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>24</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>30</v>
       </c>
@@ -2291,7 +2291,7 @@
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
     </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>191</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>354</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>12</v>
       </c>
@@ -2416,7 +2416,7 @@
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
     </row>
-    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
@@ -2455,7 +2455,7 @@
       <c r="N13" s="9"/>
       <c r="O13" s="9"/>
     </row>
-    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>324</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>32</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>33</v>
       </c>
@@ -2586,7 +2586,7 @@
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>70</v>
       </c>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>35</v>
       </c>
@@ -2672,7 +2672,7 @@
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>269</v>
       </c>
@@ -2711,7 +2711,7 @@
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>48</v>
       </c>
@@ -2750,7 +2750,7 @@
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
     </row>
-    <row r="21" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>45</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>139</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>52</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>284</v>
       </c>
@@ -2916,7 +2916,7 @@
       <c r="N24" s="9"/>
       <c r="O24" s="9"/>
     </row>
-    <row r="25" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>43</v>
       </c>
@@ -2959,7 +2959,7 @@
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
     </row>
-    <row r="26" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>55</v>
       </c>
@@ -3002,7 +3002,7 @@
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
     </row>
-    <row r="27" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>217</v>
       </c>
@@ -3043,7 +3043,7 @@
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
     </row>
-    <row r="28" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>50</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>54</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>260</v>
       </c>
@@ -3172,7 +3172,7 @@
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
     </row>
-    <row r="31" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>267</v>
       </c>
@@ -3213,7 +3213,7 @@
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>143</v>
       </c>
@@ -3254,7 +3254,7 @@
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>145</v>
       </c>
@@ -3295,7 +3295,7 @@
       <c r="N33" s="9"/>
       <c r="O33" s="9"/>
     </row>
-    <row r="34" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>147</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
     </row>
-    <row r="35" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>149</v>
       </c>
@@ -3377,7 +3377,7 @@
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
     </row>
-    <row r="36" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>57</v>
       </c>
@@ -3420,7 +3420,7 @@
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
     </row>
-    <row r="37" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>59</v>
       </c>
@@ -3463,7 +3463,7 @@
       <c r="N37" s="9"/>
       <c r="O37" s="9"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>61</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>63</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>287</v>
       </c>
@@ -3592,7 +3592,7 @@
       <c r="N40" s="9"/>
       <c r="O40" s="9"/>
     </row>
-    <row r="41" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>288</v>
       </c>
@@ -3633,7 +3633,7 @@
       <c r="N41" s="9"/>
       <c r="O41" s="9"/>
     </row>
-    <row r="42" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>67</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="N42" s="9"/>
       <c r="O42" s="9"/>
     </row>
-    <row r="43" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>208</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="N43" s="9"/>
       <c r="O43" s="9"/>
     </row>
-    <row r="44" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>69</v>
       </c>
@@ -3754,7 +3754,7 @@
       <c r="N44" s="9"/>
       <c r="O44" s="9"/>
     </row>
-    <row r="45" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>352</v>
       </c>
@@ -3793,7 +3793,7 @@
       <c r="N45" s="9"/>
       <c r="O45" s="9"/>
     </row>
-    <row r="46" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>84</v>
       </c>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O46" s="9"/>
     </row>
-    <row r="47" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>355</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>320</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>127</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>66</v>
       </c>
@@ -4002,7 +4002,7 @@
       <c r="N50" s="9"/>
       <c r="O50" s="9"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>186</v>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="N51" s="9"/>
       <c r="O51" s="9"/>
     </row>
-    <row r="52" spans="1:15" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>263</v>
       </c>
@@ -4088,7 +4088,7 @@
       <c r="N52" s="9"/>
       <c r="O52" s="9"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>366</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>365</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>37</v>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="N55" s="9"/>
       <c r="O55" s="9"/>
     </row>
-    <row r="56" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>38</v>
       </c>
@@ -4252,7 +4252,7 @@
       <c r="N56" s="9"/>
       <c r="O56" s="9"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>39</v>
       </c>
@@ -4293,7 +4293,7 @@
       <c r="N57" s="9"/>
       <c r="O57" s="9"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>76</v>
       </c>
@@ -4334,7 +4334,7 @@
       <c r="N58" s="9"/>
       <c r="O58" s="9"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>331</v>
       </c>
@@ -4375,7 +4375,7 @@
       <c r="N59" s="9"/>
       <c r="O59" s="9"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>418</v>
       </c>
@@ -4416,7 +4416,7 @@
       <c r="N60" s="9"/>
       <c r="O60" s="9"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>78</v>
       </c>
@@ -4457,7 +4457,7 @@
       <c r="N61" s="9"/>
       <c r="O61" s="9"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>80</v>
       </c>
@@ -4498,7 +4498,7 @@
       <c r="N62" s="9"/>
       <c r="O62" s="9"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>91</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>96</v>
       </c>
@@ -4582,7 +4582,7 @@
       <c r="N64" s="9"/>
       <c r="O64" s="9"/>
     </row>
-    <row r="65" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>86</v>
       </c>
@@ -4625,7 +4625,7 @@
       <c r="N65" s="9"/>
       <c r="O65" s="9"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>95</v>
       </c>
@@ -4666,7 +4666,7 @@
       <c r="N66" s="9"/>
       <c r="O66" s="9"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
         <v>98</v>
       </c>
@@ -4707,7 +4707,7 @@
       <c r="N67" s="9"/>
       <c r="O67" s="9"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>89</v>
       </c>
@@ -4748,7 +4748,7 @@
       <c r="N68" s="9"/>
       <c r="O68" s="9"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
         <v>165</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>129</v>
       </c>
@@ -4834,7 +4834,7 @@
       <c r="N70" s="9"/>
       <c r="O70" s="9"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>106</v>
       </c>
@@ -4873,7 +4873,7 @@
       <c r="N71" s="9"/>
       <c r="O71" s="9"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>329</v>
       </c>
@@ -4914,7 +4914,7 @@
       <c r="N72" s="9"/>
       <c r="O72" s="9"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
         <v>102</v>
       </c>
@@ -4955,7 +4955,7 @@
       <c r="N73" s="9"/>
       <c r="O73" s="9"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>121</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="N74" s="9"/>
       <c r="O74" s="9"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
         <v>100</v>
       </c>
@@ -5037,7 +5037,7 @@
       <c r="N75" s="9"/>
       <c r="O75" s="9"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
         <v>114</v>
       </c>
@@ -5078,7 +5078,7 @@
       <c r="N76" s="9"/>
       <c r="O76" s="9"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>116</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>108</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
         <v>118</v>
       </c>
@@ -5203,7 +5203,7 @@
       <c r="N79" s="9"/>
       <c r="O79" s="9"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
         <v>399</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
         <v>286</v>
       </c>
@@ -5287,7 +5287,7 @@
       <c r="N81" s="9"/>
       <c r="O81" s="9"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
         <v>328</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
         <v>124</v>
       </c>
@@ -5371,7 +5371,7 @@
       <c r="N83" s="9"/>
       <c r="O83" s="9"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
         <v>85</v>
       </c>
@@ -5414,7 +5414,7 @@
       <c r="N84" s="9"/>
       <c r="O84" s="9"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
         <v>190</v>
       </c>
@@ -5457,7 +5457,7 @@
       <c r="N85" s="9"/>
       <c r="O85" s="9"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
         <v>261</v>
       </c>
@@ -5500,7 +5500,7 @@
       <c r="N86" s="9"/>
       <c r="O86" s="9"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
         <v>117</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
         <v>120</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
         <v>407</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>273</v>
       </c>
@@ -5670,7 +5670,7 @@
       <c r="N90" s="9"/>
       <c r="O90" s="9"/>
     </row>
-    <row r="91" spans="1:15" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" s="3" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9" t="s">
         <v>281</v>
       </c>
@@ -5709,7 +5709,7 @@
       <c r="N91" s="9"/>
       <c r="O91" s="9"/>
     </row>
-    <row r="92" spans="1:15" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" s="3" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
         <v>40</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:15" s="3" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" s="3" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9" t="s">
         <v>304</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="N93" s="9"/>
       <c r="O93" s="9"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
         <v>210</v>
       </c>
@@ -5836,7 +5836,7 @@
       <c r="N94" s="9"/>
       <c r="O94" s="9"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="9" t="s">
         <v>125</v>
       </c>
@@ -5877,7 +5877,7 @@
       <c r="N95" s="9"/>
       <c r="O95" s="9"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>211</v>
       </c>
@@ -5918,7 +5918,7 @@
       <c r="N96" s="9"/>
       <c r="O96" s="9"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
         <v>337</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="N97" s="9"/>
       <c r="O97" s="9"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
         <v>336</v>
       </c>
@@ -6000,7 +6000,7 @@
       <c r="N98" s="9"/>
       <c r="O98" s="9"/>
     </row>
-    <row r="99" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
         <v>213</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="N99" s="9"/>
       <c r="O99" s="9"/>
     </row>
-    <row r="100" spans="1:15" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>218</v>
       </c>
@@ -6082,7 +6082,7 @@
       <c r="N100" s="9"/>
       <c r="O100" s="9"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
         <v>338</v>
       </c>
@@ -6123,7 +6123,7 @@
       <c r="N101" s="9"/>
       <c r="O101" s="9"/>
     </row>
-    <row r="102" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
         <v>339</v>
       </c>
@@ -6164,7 +6164,7 @@
       <c r="N102" s="9"/>
       <c r="O102" s="9"/>
     </row>
-    <row r="103" spans="1:15" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
         <v>72</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>358</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
         <v>74</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
         <v>356</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
         <v>75</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>359</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
         <v>131</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
         <v>112</v>
       </c>
@@ -6496,7 +6496,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
         <v>277</v>
       </c>
@@ -6535,7 +6535,7 @@
       <c r="N111" s="9"/>
       <c r="O111" s="9"/>
     </row>
-    <row r="112" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
         <v>394</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
         <v>136</v>
       </c>
@@ -6617,7 +6617,7 @@
       <c r="N113" s="9"/>
       <c r="O113" s="9"/>
     </row>
-    <row r="114" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
         <v>362</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
         <v>134</v>
       </c>
@@ -6699,7 +6699,7 @@
       <c r="N115" s="9"/>
       <c r="O115" s="9"/>
     </row>
-    <row r="116" spans="1:15" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
         <v>275</v>
       </c>
@@ -6738,7 +6738,7 @@
       <c r="N116" s="9"/>
       <c r="O116" s="9"/>
     </row>
-    <row r="117" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
         <v>221</v>
       </c>
@@ -6779,7 +6779,7 @@
       <c r="N117" s="9"/>
       <c r="O117" s="9"/>
     </row>
-    <row r="118" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>220</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="N118" s="9"/>
       <c r="O118" s="9"/>
     </row>
-    <row r="119" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="s">
         <v>333</v>
       </c>
@@ -6861,7 +6861,7 @@
       <c r="N119" s="9"/>
       <c r="O119" s="9"/>
     </row>
-    <row r="120" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>410</v>
       </c>
@@ -6902,7 +6902,7 @@
       <c r="N120" s="9"/>
       <c r="O120" s="9"/>
     </row>
-    <row r="121" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
         <v>404</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
         <v>401</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9" t="s">
         <v>138</v>
       </c>
@@ -7029,7 +7029,7 @@
       <c r="N123" s="9"/>
       <c r="O123" s="9"/>
     </row>
-    <row r="124" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
         <v>181</v>
       </c>
@@ -7072,7 +7072,7 @@
       <c r="N124" s="9"/>
       <c r="O124" s="9"/>
     </row>
-    <row r="125" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
         <v>262</v>
       </c>
@@ -7115,7 +7115,7 @@
       <c r="N125" s="9"/>
       <c r="O125" s="9"/>
     </row>
-    <row r="126" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
         <v>258</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9" t="s">
         <v>364</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
         <v>156</v>
       </c>
@@ -7242,7 +7242,7 @@
       <c r="N128" s="9"/>
       <c r="O128" s="9"/>
     </row>
-    <row r="129" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9" t="s">
         <v>175</v>
       </c>
@@ -7285,7 +7285,7 @@
       <c r="N129" s="9"/>
       <c r="O129" s="9"/>
     </row>
-    <row r="130" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>411</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="N130" s="9"/>
       <c r="O130" s="9"/>
     </row>
-    <row r="131" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
         <v>151</v>
       </c>
@@ -7371,7 +7371,7 @@
       <c r="N131" s="9"/>
       <c r="O131" s="9"/>
     </row>
-    <row r="132" spans="1:15" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
         <v>154</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9" t="s">
         <v>169</v>
       </c>
@@ -7455,7 +7455,7 @@
       <c r="N133" s="9"/>
       <c r="O133" s="9"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
         <v>219</v>
       </c>
@@ -7496,7 +7496,7 @@
       <c r="N134" s="9"/>
       <c r="O134" s="9"/>
     </row>
-    <row r="135" spans="1:15" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
         <v>341</v>
       </c>
@@ -7537,7 +7537,7 @@
       <c r="N135" s="9"/>
       <c r="O135" s="9"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
         <v>340</v>
       </c>
@@ -7578,7 +7578,7 @@
       <c r="N136" s="9"/>
       <c r="O136" s="9"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>271</v>
       </c>
@@ -7617,7 +7617,7 @@
       <c r="N137" s="9"/>
       <c r="O137" s="9"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>141</v>
       </c>
@@ -7658,7 +7658,7 @@
       <c r="N138" s="9"/>
       <c r="O138" s="9"/>
     </row>
-    <row r="139" spans="1:15" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
         <v>425</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="9" t="s">
         <v>241</v>
       </c>
@@ -7740,7 +7740,7 @@
       <c r="N140" s="9"/>
       <c r="O140" s="9"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="9" t="s">
         <v>426</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="9" t="s">
         <v>166</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="9" t="s">
         <v>167</v>
       </c>
@@ -7867,7 +7867,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="9" t="s">
         <v>168</v>
       </c>
@@ -7910,7 +7910,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="9" t="s">
         <v>8</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
         <v>77</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="9" t="s">
         <v>360</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
         <v>423</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="9" t="s">
         <v>158</v>
       </c>
@@ -8117,7 +8117,7 @@
       <c r="N149" s="9"/>
       <c r="O149" s="9"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>160</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
         <v>264</v>
       </c>
@@ -8199,7 +8199,7 @@
       <c r="N151" s="9"/>
       <c r="O151" s="9"/>
     </row>
-    <row r="152" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>82</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
         <v>361</v>
       </c>
@@ -8281,7 +8281,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="154" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
         <v>424</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9" t="s">
         <v>279</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="N155" s="9"/>
       <c r="O155" s="9"/>
     </row>
-    <row r="156" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
         <v>196</v>
       </c>
@@ -8400,7 +8400,7 @@
       <c r="N156" s="9"/>
       <c r="O156" s="9"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="9" t="s">
         <v>237</v>
       </c>
@@ -8441,7 +8441,7 @@
       <c r="N157" s="9"/>
       <c r="O157" s="9"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="9" t="s">
         <v>348</v>
       </c>
@@ -8482,7 +8482,7 @@
       <c r="N158" s="9"/>
       <c r="O158" s="9"/>
     </row>
-    <row r="159" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
         <v>349</v>
       </c>
@@ -8523,7 +8523,7 @@
       <c r="N159" s="9"/>
       <c r="O159" s="9"/>
     </row>
-    <row r="160" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>344</v>
       </c>
@@ -8564,7 +8564,7 @@
       <c r="N160" s="9"/>
       <c r="O160" s="9"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>343</v>
       </c>
@@ -8605,7 +8605,7 @@
       <c r="N161" s="9"/>
       <c r="O161" s="9"/>
     </row>
-    <row r="162" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>342</v>
       </c>
@@ -8646,7 +8646,7 @@
       <c r="N162" s="9"/>
       <c r="O162" s="9"/>
     </row>
-    <row r="163" spans="1:15" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>197</v>
       </c>
@@ -8685,7 +8685,7 @@
       <c r="N163" s="9"/>
       <c r="O163" s="9"/>
     </row>
-    <row r="164" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>238</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="165" spans="1:15" s="3" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" s="3" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>345</v>
       </c>
@@ -8769,7 +8769,7 @@
       <c r="N165" s="9"/>
       <c r="O165" s="9"/>
     </row>
-    <row r="166" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
         <v>350</v>
       </c>
@@ -8810,7 +8810,7 @@
       <c r="N166" s="9"/>
       <c r="O166" s="9"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="s">
         <v>419</v>
       </c>
@@ -8851,7 +8851,7 @@
       <c r="N167" s="9"/>
       <c r="O167" s="9"/>
     </row>
-    <row r="168" spans="1:15" ht="73.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
         <v>420</v>
       </c>
@@ -8892,7 +8892,7 @@
       <c r="N168" s="9"/>
       <c r="O168" s="9"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
         <v>421</v>
       </c>
@@ -8933,7 +8933,7 @@
       <c r="N169" s="9"/>
       <c r="O169" s="9"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
         <v>412</v>
       </c>
@@ -8972,7 +8972,7 @@
       <c r="N170" s="9"/>
       <c r="O170" s="9"/>
     </row>
-    <row r="171" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="9" t="s">
         <v>413</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>422</v>
       </c>
@@ -9056,7 +9056,7 @@
       <c r="N172" s="9"/>
       <c r="O172" s="9"/>
     </row>
-    <row r="173" spans="1:15" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" s="3" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
         <v>432</v>
       </c>
